--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_TRWIP-CSTD-0-00-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_TRWIP-CSTD-0-00-B-C0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF176761-A7FA-4027-AAC5-F57B93CD4FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD382FF2-0C29-44D5-AB1E-7C67F8066A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3255" yWindow="1095" windowWidth="22740" windowHeight="14070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -526,7 +526,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2570" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2572" uniqueCount="284">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2957,6 +2957,25 @@
   <si>
     <t>－</t>
   </si>
+  <si>
+    <t>1.3.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4298,7 +4317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="281">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4932,6 +4951,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4962,37 +5011,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5037,10 +5065,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5094,34 +5143,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="77" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7388,6 +7413,188 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>173180</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>173180</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C0D05F-62C5-439D-A223-53AAAAC831CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13386956" y="900544"/>
+          <a:ext cx="831272" cy="4849091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E184700-5DFC-40A1-957C-3D2C52C89AFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15603681" y="15967363"/>
+          <a:ext cx="18010910" cy="6407727"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7698,18 +7905,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="218" t="s">
+      <c r="I2" s="228" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="218"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="218"/>
-      <c r="M2" s="218"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="218"/>
+      <c r="J2" s="228"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="228"/>
+      <c r="M2" s="228"/>
+      <c r="N2" s="228"/>
+      <c r="O2" s="228"/>
+      <c r="P2" s="228"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="228"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -7722,25 +7929,25 @@
       <c r="H3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="I3" s="219" t="s">
+      <c r="I3" s="229" t="s">
         <v>191</v>
       </c>
-      <c r="J3" s="220"/>
-      <c r="K3" s="220"/>
-      <c r="L3" s="220"/>
-      <c r="M3" s="220"/>
-      <c r="N3" s="220"/>
-      <c r="O3" s="220"/>
-      <c r="P3" s="220"/>
-      <c r="Q3" s="220"/>
-      <c r="R3" s="220"/>
+      <c r="J3" s="230"/>
+      <c r="K3" s="230"/>
+      <c r="L3" s="230"/>
+      <c r="M3" s="230"/>
+      <c r="N3" s="230"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="230"/>
+      <c r="Q3" s="230"/>
+      <c r="R3" s="230"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="23" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.2.0</v>
+        <v>1.3.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -7754,43 +7961,43 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="213" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="214"/>
-      <c r="E7" s="215" t="s">
+      <c r="C7" s="223" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="224"/>
+      <c r="E7" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="215"/>
-      <c r="G7" s="216" t="s">
+      <c r="F7" s="225"/>
+      <c r="G7" s="226" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="217" t="s">
+      <c r="H7" s="226"/>
+      <c r="I7" s="226"/>
+      <c r="J7" s="226"/>
+      <c r="K7" s="226"/>
+      <c r="L7" s="226"/>
+      <c r="M7" s="227" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="217"/>
-      <c r="O7" s="217"/>
-      <c r="P7" s="217"/>
-      <c r="Q7" s="217"/>
-      <c r="R7" s="217"/>
-      <c r="S7" s="269" t="s">
+      <c r="N7" s="227"/>
+      <c r="O7" s="227"/>
+      <c r="P7" s="227"/>
+      <c r="Q7" s="227"/>
+      <c r="R7" s="227"/>
+      <c r="S7" s="220" t="s">
         <v>275</v>
       </c>
-      <c r="T7" s="270"/>
-      <c r="U7" s="270"/>
-      <c r="V7" s="270"/>
-      <c r="W7" s="270"/>
-      <c r="X7" s="271"/>
+      <c r="T7" s="221"/>
+      <c r="U7" s="221"/>
+      <c r="V7" s="221"/>
+      <c r="W7" s="221"/>
+      <c r="X7" s="222"/>
     </row>
     <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
@@ -7844,7 +8051,7 @@
       <c r="R8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="S8" s="272" t="s">
+      <c r="S8" s="213" t="s">
         <v>276</v>
       </c>
       <c r="T8" s="16" t="s">
@@ -7859,7 +8066,7 @@
       <c r="W8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="X8" s="273" t="s">
+      <c r="X8" s="214" t="s">
         <v>11</v>
       </c>
     </row>
@@ -7905,10 +8112,10 @@
       <c r="Q9" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="R9" s="277">
+      <c r="R9" s="218">
         <v>44257</v>
       </c>
-      <c r="S9" s="274" t="s">
+      <c r="S9" s="215" t="s">
         <v>277</v>
       </c>
       <c r="T9" s="1" t="s">
@@ -7923,7 +8130,7 @@
       <c r="W9" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="X9" s="275" t="s">
+      <c r="X9" s="216" t="s">
         <v>277</v>
       </c>
     </row>
@@ -7969,10 +8176,10 @@
       <c r="Q10" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="R10" s="278">
+      <c r="R10" s="219">
         <v>44846</v>
       </c>
-      <c r="S10" s="274" t="s">
+      <c r="S10" s="215" t="s">
         <v>277</v>
       </c>
       <c r="T10" s="1" t="s">
@@ -8026,25 +8233,25 @@
       <c r="L11" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="M11" s="274" t="s">
+      <c r="M11" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="N11" s="274" t="s">
+      <c r="N11" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="O11" s="274" t="s">
+      <c r="O11" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="P11" s="274" t="s">
+      <c r="P11" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="Q11" s="274" t="s">
+      <c r="Q11" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="R11" s="274" t="s">
+      <c r="R11" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="S11" s="274" t="s">
+      <c r="S11" s="215" t="s">
         <v>277</v>
       </c>
       <c r="T11" s="1" t="s">
@@ -8063,13 +8270,17 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:24" ht="40.5">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="C12" s="280" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" s="279" t="s">
+        <v>283</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -8084,7 +8295,7 @@
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="274"/>
+      <c r="S12" s="215"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
@@ -8112,7 +8323,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="276"/>
+      <c r="S13" s="217"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
@@ -8121,13 +8332,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="I2:R2"/>
+    <mergeCell ref="I3:R3"/>
     <mergeCell ref="S7:X7"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="G7:L7"/>
     <mergeCell ref="M7:R7"/>
-    <mergeCell ref="I2:R2"/>
-    <mergeCell ref="I3:R3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
@@ -8406,15 +8617,15 @@
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="221"/>
-      <c r="D38" s="222"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="232"/>
       <c r="E38" s="114" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="223"/>
-      <c r="D39" s="224"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="234"/>
       <c r="E39" s="5" t="s">
         <v>125</v>
       </c>
@@ -8454,44 +8665,44 @@
   <sheetData>
     <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="235" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="251"/>
-      <c r="D2" s="238" t="s">
+      <c r="C2" s="236"/>
+      <c r="D2" s="241" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="225" t="s">
+      <c r="B3" s="237" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="226"/>
-      <c r="D3" s="241" t="s">
+      <c r="C3" s="238"/>
+      <c r="D3" s="244" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="243"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="245"/>
+      <c r="H3" s="246"/>
     </row>
     <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="236" t="s">
+      <c r="B4" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="D4" s="244" t="str">
+      <c r="C4" s="240"/>
+      <c r="D4" s="247" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_TRWIP-CSTD-0-00-B-C0.c</v>
       </c>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="246"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="249"/>
     </row>
     <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
@@ -8500,70 +8711,70 @@
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="250" t="s">
+      <c r="B6" s="235" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="251"/>
-      <c r="D6" s="247" t="str">
+      <c r="C6" s="236"/>
+      <c r="D6" s="250" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_TRWIP</v>
       </c>
-      <c r="E6" s="248"/>
-      <c r="F6" s="248"/>
-      <c r="G6" s="248"/>
-      <c r="H6" s="249"/>
+      <c r="E6" s="251"/>
+      <c r="F6" s="251"/>
+      <c r="G6" s="251"/>
+      <c r="H6" s="252"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="225" t="s">
+      <c r="B7" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="226"/>
-      <c r="D7" s="227">
+      <c r="C7" s="238"/>
+      <c r="D7" s="253">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="228"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="228"/>
-      <c r="H7" s="229"/>
+      <c r="E7" s="254"/>
+      <c r="F7" s="254"/>
+      <c r="G7" s="254"/>
+      <c r="H7" s="255"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="237" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="226"/>
-      <c r="D8" s="227" t="str">
+      <c r="C8" s="238"/>
+      <c r="D8" s="253" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_TRWIP_MTRX</v>
       </c>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="228"/>
-      <c r="H8" s="229"/>
+      <c r="E8" s="254"/>
+      <c r="F8" s="254"/>
+      <c r="G8" s="254"/>
+      <c r="H8" s="255"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="225" t="s">
+      <c r="B9" s="237" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="226"/>
-      <c r="D9" s="230" t="s">
+      <c r="C9" s="238"/>
+      <c r="D9" s="256" t="s">
         <v>237</v>
       </c>
-      <c r="E9" s="231"/>
-      <c r="F9" s="231"/>
-      <c r="G9" s="231"/>
-      <c r="H9" s="232"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="258"/>
     </row>
     <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="236" t="s">
+      <c r="B10" s="239" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="237"/>
-      <c r="D10" s="233"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="234"/>
-      <c r="G10" s="234"/>
-      <c r="H10" s="235"/>
+      <c r="C10" s="240"/>
+      <c r="D10" s="259"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="260"/>
+      <c r="H10" s="261"/>
     </row>
     <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="12" spans="2:14" ht="14.25" thickBot="1">
@@ -9495,22 +9706,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -13542,7 +13753,7 @@
       <c r="B2" s="128" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="252" t="s">
+      <c r="C2" s="262" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="59">
@@ -13641,7 +13852,7 @@
       <c r="AI2" s="59">
         <v>0</v>
       </c>
-      <c r="AJ2" s="254" t="s">
+      <c r="AJ2" s="264" t="s">
         <v>162</v>
       </c>
     </row>
@@ -13650,7 +13861,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="253"/>
+      <c r="C3" s="263"/>
       <c r="D3" s="130" t="s">
         <v>61</v>
       </c>
@@ -13741,20 +13952,20 @@
       <c r="AG3" s="202" t="s">
         <v>240</v>
       </c>
-      <c r="AH3" s="260" t="s">
+      <c r="AH3" s="270" t="s">
         <v>241</v>
       </c>
-      <c r="AI3" s="261"/>
-      <c r="AJ3" s="255"/>
+      <c r="AI3" s="271"/>
+      <c r="AJ3" s="265"/>
       <c r="AR3" s="92" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="256" t="s">
+      <c r="A4" s="266" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="257"/>
+      <c r="B4" s="267"/>
       <c r="C4" s="140"/>
       <c r="D4" s="140"/>
       <c r="E4" s="140"/>
@@ -13799,8 +14010,8 @@
       <c r="AW4" s="82"/>
     </row>
     <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="258"/>
-      <c r="B5" s="259"/>
+      <c r="A5" s="268"/>
+      <c r="B5" s="269"/>
       <c r="C5" s="141"/>
       <c r="D5" s="141"/>
       <c r="E5" s="141"/>
@@ -42327,16 +42538,16 @@
       <c r="B3" s="96" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="276" t="s">
         <v>225</v>
       </c>
-      <c r="D3" s="267"/>
-      <c r="E3" s="267"/>
-      <c r="F3" s="267"/>
-      <c r="G3" s="267"/>
-      <c r="H3" s="267"/>
-      <c r="I3" s="267"/>
-      <c r="J3" s="268"/>
+      <c r="D3" s="277"/>
+      <c r="E3" s="277"/>
+      <c r="F3" s="277"/>
+      <c r="G3" s="277"/>
+      <c r="H3" s="277"/>
+      <c r="I3" s="277"/>
+      <c r="J3" s="278"/>
       <c r="K3" s="171"/>
       <c r="L3" s="171"/>
       <c r="M3" s="174"/>
@@ -42376,16 +42587,16 @@
       <c r="B5" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="262" t="s">
+      <c r="C5" s="272" t="s">
         <v>186</v>
       </c>
-      <c r="D5" s="263"/>
-      <c r="E5" s="263"/>
-      <c r="F5" s="263"/>
-      <c r="G5" s="263"/>
-      <c r="H5" s="263"/>
-      <c r="I5" s="263"/>
-      <c r="J5" s="264"/>
+      <c r="D5" s="273"/>
+      <c r="E5" s="273"/>
+      <c r="F5" s="273"/>
+      <c r="G5" s="273"/>
+      <c r="H5" s="273"/>
+      <c r="I5" s="273"/>
+      <c r="J5" s="274"/>
       <c r="K5" s="35" t="s">
         <v>23</v>
       </c>
@@ -42456,16 +42667,16 @@
       <c r="B7" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="265" t="s">
+      <c r="C7" s="275" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="263"/>
-      <c r="E7" s="263"/>
-      <c r="F7" s="263"/>
-      <c r="G7" s="263"/>
-      <c r="H7" s="263"/>
-      <c r="I7" s="263"/>
-      <c r="J7" s="264"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="273"/>
+      <c r="G7" s="273"/>
+      <c r="H7" s="273"/>
+      <c r="I7" s="273"/>
+      <c r="J7" s="274"/>
       <c r="K7" s="198" t="s">
         <v>239</v>
       </c>
